--- a/documents/Työajan-seuranta-Ryhmä10.xlsx
+++ b/documents/Työajan-seuranta-Ryhmä10.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29816"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleks\Desktop\Tylypahka\OAMK\Codes\Food-Waste-Tracker\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04EA5D07-C2E0-4AAA-92E6-D89166D4F3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="165" documentId="13_ncr:1_{04EA5D07-C2E0-4AAA-92E6-D89166D4F3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FB45C5B-E9F7-4CDD-ACED-2F3C0E764046}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="1" activeTab="1" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Aleksi Huotari" sheetId="1" r:id="rId1"/>
-    <sheet name="Antti Ahkera" sheetId="3" r:id="rId2"/>
+    <sheet name="Mikhail Roulinski" sheetId="3" r:id="rId2"/>
     <sheet name="Teppo Terävä" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="52">
+  <si>
+    <t>Ryhmä:</t>
+  </si>
   <si>
     <t>Pvm</t>
   </si>
@@ -46,101 +49,170 @@
     <t>Tehtävä</t>
   </si>
   <si>
-    <t>Ryhmä:</t>
-  </si>
-  <si>
-    <t>Antti Ahkera</t>
+    <t>Aleksi Huotari</t>
+  </si>
+  <si>
+    <t>Moqup</t>
+  </si>
+  <si>
+    <t>Ominaisuuksien suunnittelu</t>
+  </si>
+  <si>
+    <t>Tietokannan suunnittelu</t>
+  </si>
+  <si>
+    <t>Tietokannan suunnittelu ja toteutus</t>
+  </si>
+  <si>
+    <t>Waste report ominaisuuden suunnittelu</t>
+  </si>
+  <si>
+    <t>Waste report devaus</t>
+  </si>
+  <si>
+    <t>Waste report devaus + pr</t>
+  </si>
+  <si>
+    <t>Reports ominaisuuden suunnittelu</t>
+  </si>
+  <si>
+    <t>Reports devaus</t>
+  </si>
+  <si>
+    <t>Reports devaus + PR</t>
+  </si>
+  <si>
+    <t>Menu ominaisuuden suunnittelu + devaus</t>
+  </si>
+  <si>
+    <t>Menu devaus</t>
+  </si>
+  <si>
+    <t>GPS funktion tutkiminen + devaus</t>
+  </si>
+  <si>
+    <t>GPS devaus</t>
+  </si>
+  <si>
+    <t>Advanced mobile tehtävän tutkiminen</t>
+  </si>
+  <si>
+    <t>Advanced mobile idean suunnittelu</t>
+  </si>
+  <si>
+    <t>Yleistä debuggausta</t>
+  </si>
+  <si>
+    <t>Quick Notes functio + PR</t>
+  </si>
+  <si>
+    <t>Dokumentaation kasaus + bugi korjaukset</t>
+  </si>
+  <si>
+    <t>RSS linkkien korjaus sivusto muutoksien vuoksi</t>
+  </si>
+  <si>
+    <t>Yhteensä</t>
+  </si>
+  <si>
+    <t>Mikhail Roulinski</t>
+  </si>
+  <si>
+    <t>Projektin suunnittelua ja perehtyminen</t>
+  </si>
+  <si>
+    <t>Scrum Master tehtävät</t>
+  </si>
+  <si>
+    <t>Suunnittelua</t>
+  </si>
+  <si>
+    <t>Scrummi</t>
+  </si>
+  <si>
+    <t>Navigaatio ja Valikot</t>
+  </si>
+  <si>
+    <t>Scrum</t>
+  </si>
+  <si>
+    <t>Alivalikot</t>
+  </si>
+  <si>
+    <t>Complaints - ominaisuuksien suunnittelu</t>
+  </si>
+  <si>
+    <t>Complaints - ominaisuuksien toteutus</t>
+  </si>
+  <si>
+    <t>Complaints testailu</t>
+  </si>
+  <si>
+    <t>Authentikointi- sunnittelu</t>
+  </si>
+  <si>
+    <t>Authentikointi- suunnittelu</t>
+  </si>
+  <si>
+    <t>Authentikointi- toteutus</t>
+  </si>
+  <si>
+    <t>Authentikointi- toteutus ja testailu</t>
+  </si>
+  <si>
+    <t>Notifications &amp; Push Token - suunnittelu</t>
+  </si>
+  <si>
+    <t>Advance-mobile</t>
+  </si>
+  <si>
+    <t>Notifications &amp; Push Token</t>
+  </si>
+  <si>
+    <t>Notifications &amp; Push Token + debug</t>
+  </si>
+  <si>
+    <t>Arkkitehtuurin selvennys esitystä varten</t>
+  </si>
+  <si>
+    <t>Arkkitehtuurin selvennys esitystä varten + debug</t>
+  </si>
+  <si>
+    <t>Testailu Notificaatiot ja Push Notify</t>
+  </si>
+  <si>
+    <t>Testailu - EAS -&gt; Preview - Build</t>
+  </si>
+  <si>
+    <t>Advance-mobile esityksen valmistelu</t>
+  </si>
+  <si>
+    <t>Yhteensä:</t>
   </si>
   <si>
     <t>Teppo Terävä</t>
   </si>
   <si>
-    <t>Käyttöliitymän suunnittelu</t>
-  </si>
-  <si>
-    <t>Arvosanan luku käyttöliittymän teko</t>
-  </si>
-  <si>
     <t>Tulostusrutiinin teko</t>
-  </si>
-  <si>
-    <t>Aleksi Huotari</t>
-  </si>
-  <si>
-    <t>Moqup</t>
-  </si>
-  <si>
-    <t>Ominaisuuksien suunnittelu</t>
-  </si>
-  <si>
-    <t>Tietokannan suunnittelu</t>
-  </si>
-  <si>
-    <t>Waste report ominaisuuden suunnittelu</t>
-  </si>
-  <si>
-    <t>Waste report devaus</t>
-  </si>
-  <si>
-    <t>Waste report devaus + pr</t>
-  </si>
-  <si>
-    <t>Reports ominaisuuden suunnittelu</t>
-  </si>
-  <si>
-    <t>Reports devaus</t>
-  </si>
-  <si>
-    <t>Reports devaus + PR</t>
-  </si>
-  <si>
-    <t>Menu ominaisuuden suunnittelu + devaus</t>
-  </si>
-  <si>
-    <t>Menu devaus</t>
-  </si>
-  <si>
-    <t>Tietokannan suunnittelu ja toteutus</t>
-  </si>
-  <si>
-    <t>GPS funktion tutkiminen + devaus</t>
-  </si>
-  <si>
-    <t>GPS devaus</t>
-  </si>
-  <si>
-    <t>Advanced mobile tehtävän tutkiminen</t>
-  </si>
-  <si>
-    <t>Advanced mobile idean suunnittelu</t>
-  </si>
-  <si>
-    <t>Yhteensä</t>
-  </si>
-  <si>
-    <t>Yleistä debuggausta</t>
-  </si>
-  <si>
-    <t>Quick Notes functio + PR</t>
-  </si>
-  <si>
-    <t>Dokumentaation kasaus + bugi korjaukset</t>
-  </si>
-  <si>
-    <t>RSS linkkien korjaus sivusto muutoksien vuoksi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -163,9 +235,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -184,9 +257,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -224,7 +297,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -330,7 +403,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -472,7 +545,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -481,310 +554,310 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BD4D073-EB2D-44A2-86BF-660E3721AF80}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="6" width="13.1796875" customWidth="1"/>
+    <col min="3" max="6" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1">
         <v>46029.1</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3">
       <c r="A4" s="1">
         <v>46030.1</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3">
       <c r="A5" s="1">
         <v>46033.1</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3">
       <c r="A6" s="1">
         <v>46034.1</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3">
       <c r="A7" s="1">
         <v>46036.1</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3">
       <c r="A8" s="1">
         <v>46037.1</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3">
       <c r="A9" s="1">
         <v>46038.1</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3">
       <c r="A10" s="1">
         <v>46039.1</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C10">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3">
       <c r="A11" s="1">
         <v>46040.1</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C11">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3">
       <c r="A12" s="1">
         <v>46042.1</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3">
       <c r="A13" s="1">
         <v>46043.1</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C13">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3">
       <c r="A14" s="1">
         <v>46044.1</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3">
       <c r="A15" s="1">
         <v>46045.1</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C15">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3">
       <c r="A16" s="1">
         <v>46046.1</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C16">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3">
       <c r="A17" s="1">
         <v>46048.1</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3">
       <c r="A18" s="1">
         <v>46049.1</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C18">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3">
       <c r="A19" s="1">
         <v>46050.1</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C19">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3">
       <c r="A20" s="1">
         <v>46051.1</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C20">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3">
       <c r="A21" s="1">
         <v>46052.1</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C21">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3">
       <c r="A22" s="1">
         <v>46056.1</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3">
       <c r="A23" s="1">
         <v>46057.1</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3">
       <c r="A24" s="1">
         <v>46061.1</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C24">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3">
       <c r="A25" s="1">
         <v>46062.1</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C25">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3">
       <c r="A26" s="1">
         <v>46066.1</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C26">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3">
       <c r="A27" s="1">
         <v>46073.1</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C31">
         <f>SUM(C3:C27)</f>
@@ -798,58 +871,375 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C1EECD9-4AD3-41AF-8923-B28678799497}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C39"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" customWidth="1"/>
-    <col min="2" max="2" width="31.36328125" customWidth="1"/>
-    <col min="3" max="3" width="11.36328125" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="45.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1">
+        <v>46030</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1">
+        <v>46035</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1">
+        <v>46035</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1">
+        <v>46040</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
-        <v>45209</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13">
         <v>5</v>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
-        <v>45210</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="1"/>
-    </row>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1">
+        <v>46048</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1">
+        <v>46050</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1">
+        <v>46054</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="1">
+        <v>46056</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="1">
+        <v>46057</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15">
+      <c r="A19" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="1">
+        <v>46059</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="1">
+        <v>46059</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="1">
+        <v>46060</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="1">
+        <v>46061</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="1">
+        <v>46064</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="1">
+        <v>46066</v>
+      </c>
+      <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="1">
+        <v>46067</v>
+      </c>
+      <c r="B27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15">
+      <c r="A28" s="1">
+        <v>46067</v>
+      </c>
+      <c r="B28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="1">
+        <v>46070</v>
+      </c>
+      <c r="B29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="1">
+        <v>46071</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="1">
+        <v>46073</v>
+      </c>
+      <c r="B32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="C34">
+        <f>SUM(C4:C32)</f>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -858,49 +1248,49 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74BC3D70-9A8B-4A59-8343-1D3356DFB267}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="9.81640625" customWidth="1"/>
-    <col min="2" max="2" width="30.81640625" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1">
         <v>45211</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="C3">
         <v>3.5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3">
       <c r="A4" s="1">
         <v>45213</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="C4">
         <v>4.5</v>

--- a/documents/Työajan-seuranta-Ryhmä10.xlsx
+++ b/documents/Työajan-seuranta-Ryhmä10.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleks\Desktop\Tylypahka\OAMK\Codes\Food-Waste-Tracker\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FoodWasteTracker\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="165" documentId="13_ncr:1_{04EA5D07-C2E0-4AAA-92E6-D89166D4F3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FB45C5B-E9F7-4CDD-ACED-2F3C0E764046}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0756D3AD-740C-4AFB-AC86-7A84662606AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="1" activeTab="1" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Aleksi Huotari" sheetId="1" r:id="rId1"/>
     <sheet name="Mikhail Roulinski" sheetId="3" r:id="rId2"/>
-    <sheet name="Teppo Terävä" sheetId="4" r:id="rId3"/>
+    <sheet name="Niko Hostikka" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
   <si>
     <t>Ryhmä:</t>
   </si>
@@ -190,17 +190,74 @@
     <t>Yhteensä:</t>
   </si>
   <si>
-    <t>Teppo Terävä</t>
-  </si>
-  <si>
-    <t>Tulostusrutiinin teko</t>
+    <t>Niko Hostikka</t>
+  </si>
+  <si>
+    <t>Projektin suunnittelu</t>
+  </si>
+  <si>
+    <t>Scrum palaveri</t>
+  </si>
+  <si>
+    <t>Yleisnäkymän suunnittelu</t>
+  </si>
+  <si>
+    <t>Käyttäjämäärittely</t>
+  </si>
+  <si>
+    <t>Työntekijän hallinta</t>
+  </si>
+  <si>
+    <t>Projektin suunnittelu, Asetukset</t>
+  </si>
+  <si>
+    <t>Dark Mode, Profiilikuvat</t>
+  </si>
+  <si>
+    <t>Kieliasetukset</t>
+  </si>
+  <si>
+    <t>Supabase integraatio, kieliasetukset</t>
+  </si>
+  <si>
+    <t>Kovakoodattujen määritysten muokkaus</t>
+  </si>
+  <si>
+    <t>Dark Mode päivitykset</t>
+  </si>
+  <si>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>Projektin suunnittelu, settings</t>
+  </si>
+  <si>
+    <t>Dokumentointi, bugien korjaus</t>
+  </si>
+  <si>
+    <t>Videon käsikirjoitus</t>
+  </si>
+  <si>
+    <t>Videon käsikirjoitus, testaus</t>
+  </si>
+  <si>
+    <t>Videon suunnittelu, kuvaus</t>
+  </si>
+  <si>
+    <t>Videon suunnittelu, editointi, dokumentointi</t>
+  </si>
+  <si>
+    <t>Videon editointi ja julkaisu, dokumentointi</t>
+  </si>
+  <si>
+    <t>YHT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,10 +292,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -257,9 +316,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -297,7 +356,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -403,7 +462,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -545,7 +604,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -554,14 +613,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BD4D073-EB2D-44A2-86BF-660E3721AF80}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
     <col min="3" max="6" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -569,7 +628,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -580,7 +639,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46029.1</v>
       </c>
@@ -591,7 +650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46030.1</v>
       </c>
@@ -602,7 +661,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46033.1</v>
       </c>
@@ -613,7 +672,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46034.1</v>
       </c>
@@ -624,7 +683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46036.1</v>
       </c>
@@ -635,7 +694,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46037.1</v>
       </c>
@@ -646,7 +705,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46038.1</v>
       </c>
@@ -657,7 +716,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46039.1</v>
       </c>
@@ -668,7 +727,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46040.1</v>
       </c>
@@ -679,7 +738,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46042.1</v>
       </c>
@@ -690,7 +749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46043.1</v>
       </c>
@@ -701,7 +760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46044.1</v>
       </c>
@@ -712,7 +771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46045.1</v>
       </c>
@@ -723,7 +782,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46046.1</v>
       </c>
@@ -734,7 +793,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46048.1</v>
       </c>
@@ -745,7 +804,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46049.1</v>
       </c>
@@ -756,7 +815,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46050.1</v>
       </c>
@@ -767,7 +826,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46051.1</v>
       </c>
@@ -778,7 +837,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46052.1</v>
       </c>
@@ -789,7 +848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46056.1</v>
       </c>
@@ -800,7 +859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46057.1</v>
       </c>
@@ -811,7 +870,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46061.1</v>
       </c>
@@ -822,7 +881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46062.1</v>
       </c>
@@ -833,7 +892,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46066.1</v>
       </c>
@@ -844,7 +903,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46073.1</v>
       </c>
@@ -855,7 +914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -871,15 +930,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C1EECD9-4AD3-41AF-8923-B28678799497}">
-  <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
     <col min="2" max="2" width="45.85546875" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -887,7 +946,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -898,7 +957,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46030</v>
       </c>
@@ -909,7 +968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46031</v>
       </c>
@@ -920,7 +979,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46035</v>
       </c>
@@ -931,7 +990,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46035</v>
       </c>
@@ -942,7 +1001,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46036</v>
       </c>
@@ -953,7 +1012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46039</v>
       </c>
@@ -964,7 +1023,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46040</v>
       </c>
@@ -975,7 +1034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46041</v>
       </c>
@@ -986,7 +1045,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46042</v>
       </c>
@@ -997,7 +1056,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46043</v>
       </c>
@@ -1008,7 +1067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46045</v>
       </c>
@@ -1019,7 +1078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46048</v>
       </c>
@@ -1030,7 +1089,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46050</v>
       </c>
@@ -1041,7 +1100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46054</v>
       </c>
@@ -1052,7 +1111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46056</v>
       </c>
@@ -1063,7 +1122,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46057</v>
       </c>
@@ -1074,7 +1133,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46058</v>
       </c>
@@ -1085,7 +1144,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46059</v>
       </c>
@@ -1096,7 +1155,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46059</v>
       </c>
@@ -1107,7 +1166,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46060</v>
       </c>
@@ -1118,7 +1177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46061</v>
       </c>
@@ -1129,7 +1188,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46064</v>
       </c>
@@ -1140,7 +1199,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46065</v>
       </c>
@@ -1151,7 +1210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46066</v>
       </c>
@@ -1162,7 +1221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46067</v>
       </c>
@@ -1173,7 +1232,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46067</v>
       </c>
@@ -1184,7 +1243,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46070</v>
       </c>
@@ -1195,7 +1254,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46071</v>
       </c>
@@ -1206,7 +1265,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46072</v>
       </c>
@@ -1217,7 +1276,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46073</v>
       </c>
@@ -1228,18 +1287,17 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C34">
         <f>SUM(C4:C32)</f>
         <v>110</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1247,53 +1305,300 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74BC3D70-9A8B-4A59-8343-1D3356DFB267}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" customWidth="1"/>
+    <col min="2" max="2" width="43.7109375" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="B1" s="3">
+        <v>10</v>
+      </c>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1">
-        <v>45211</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>46028</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="3">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>46030</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>46033</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>46034</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="3">
         <v>3.5</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1">
-        <v>45213</v>
-      </c>
-      <c r="B4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>46035</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>46039</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>46045</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>46048</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="3">
         <v>4.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>46050</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="3">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>46054</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="3">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>46055</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>46056</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>46059</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="3">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>46060</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>46064</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>46065</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>46067</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>46068</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>46072</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>46073</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="3">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>46074</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="3">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3">
+        <f>SUM(C3:C25)</f>
+        <v>76.5</v>
       </c>
     </row>
   </sheetData>
